--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:13</t>
+    <t xml:space="preserve">2026-09-09 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:08</t>
+    <t xml:space="preserve">2026-09-17 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:04</t>
+    <t xml:space="preserve">2026-09-23 12:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:33</t>
+    <t xml:space="preserve">2026-10-02 13:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:32</t>
+    <t xml:space="preserve">2026-10-05 10:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -637,7 +637,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>801671.62</v>
+        <v>801671.63</v>
       </c>
     </row>
     <row r="3">
@@ -1113,7 +1113,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>308235.62</v>
+        <v>308235.63</v>
       </c>
     </row>
     <row r="31">
@@ -1470,7 +1470,7 @@
         <v>2018</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>218680.62</v>
+        <v>218680.63</v>
       </c>
     </row>
     <row r="52">
